--- a/data/trans_bre/IP18A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 7,37</t>
+          <t>-12,17; 7,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 16,47</t>
+          <t>-3,75; 16,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 12,9</t>
+          <t>-11,43; 12,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 34,99</t>
+          <t>-13,66; 34,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,71; 49,35</t>
+          <t>-46,72; 54,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 138,16</t>
+          <t>-18,88; 136,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,97; 94,06</t>
+          <t>-47,34; 93,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 8,8</t>
+          <t>-0,62; 8,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,76</t>
+          <t>0,05; 9,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 2,1</t>
+          <t>-6,19; 2,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 14,13</t>
+          <t>-9,24; 12,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 53,61</t>
+          <t>-3,24; 53,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 57,44</t>
+          <t>0,04; 58,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 12,23</t>
+          <t>-28,87; 14,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 89,94</t>
+          <t>-38,24; 73,94</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 10,94</t>
+          <t>-4,63; 11,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,96</t>
+          <t>-12,97; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 11,76</t>
+          <t>-3,69; 12,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 7,58</t>
+          <t>-20,95; 6,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 55,25</t>
+          <t>-16,05; 56,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 8,24</t>
+          <t>-48,13; 9,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 69,64</t>
+          <t>-15,89; 73,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,25; 119,71</t>
+          <t>-82,64; 83,55</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,03</t>
+          <t>-0,78; 7,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 5,68</t>
+          <t>-1,09; 6,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,25</t>
+          <t>-3,93; 2,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 10,24</t>
+          <t>-8,02; 8,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 38,17</t>
+          <t>-3,35; 38,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 33,52</t>
+          <t>-5,36; 37,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 19,2</t>
+          <t>-18,51; 15,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 69,03</t>
+          <t>-35,03; 56,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 7,8</t>
+          <t>-12,4; 8,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 16,16</t>
+          <t>-4,36; 16,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 12,74</t>
+          <t>-11,36; 11,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 34,82</t>
+          <t>-14,31; 32,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,72; 54,02</t>
+          <t>-50,2; 57,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 136,39</t>
+          <t>-19,49; 129,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 93,8</t>
+          <t>-45,89; 85,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 8,73</t>
+          <t>-0,52; 8,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 9,01</t>
+          <t>0,23; 9,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 2,4</t>
+          <t>-6,57; 2,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 12,66</t>
+          <t>-9,43; 13,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 53,24</t>
+          <t>-2,4; 51,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 58,87</t>
+          <t>1,11; 59,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 14,09</t>
+          <t>-29,3; 13,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 73,94</t>
+          <t>-36,18; 81,46</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 11,39</t>
+          <t>-5,82; 10,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 1,9</t>
+          <t>-13,75; 1,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 12,02</t>
+          <t>-3,64; 10,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 6,2</t>
+          <t>-21,19; 6,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 56,02</t>
+          <t>-19,41; 53,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,13; 9,27</t>
+          <t>-50,28; 8,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 73,98</t>
+          <t>-16,84; 63,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,64; 83,55</t>
+          <t>-84,84; 87,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 7,01</t>
+          <t>-0,53; 6,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 6,45</t>
+          <t>-1,15; 5,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,79</t>
+          <t>-3,76; 3,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 8,7</t>
+          <t>-8,11; 9,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 38,4</t>
+          <t>-2,39; 37,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 37,24</t>
+          <t>-5,56; 33,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 15,8</t>
+          <t>-17,62; 19,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 56,66</t>
+          <t>-36,46; 62,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>117,85%</t>
+          <t>116,67%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 8,18</t>
+          <t>-14,76; 7,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 16,19</t>
+          <t>-3,75; 16,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 11,88</t>
+          <t>-12,16; 12,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 32,67</t>
+          <t>-13,77; 34,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,2; 57,92</t>
+          <t>-54,71; 49,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 129,75</t>
+          <t>-16,98; 138,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 85,31</t>
+          <t>-48,97; 94,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 8,49</t>
+          <t>-0,73; 8,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,42</t>
+          <t>0,12; 8,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 2,38</t>
+          <t>-6,11; 2,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 13,44</t>
+          <t>-9,29; 16,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 51,57</t>
+          <t>-3,72; 53,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 59,66</t>
+          <t>0,57; 57,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 13,95</t>
+          <t>-28,62; 12,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 81,46</t>
+          <t>-36,7; 95,04</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,51</t>
+          <t>-5,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-38,18%</t>
+          <t>-34,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 10,73</t>
+          <t>-5,53; 10,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 1,59</t>
+          <t>-14,0; 0,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 10,52</t>
+          <t>-4,09; 11,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 6,88</t>
+          <t>-19,73; 9,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 53,88</t>
+          <t>-18,99; 55,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 8,39</t>
+          <t>-49,54; 8,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 63,11</t>
+          <t>-18,32; 69,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-84,84; 87,49</t>
+          <t>-79,29; 134,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 6,91</t>
+          <t>-0,62; 7,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,64</t>
+          <t>-1,46; 5,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,35</t>
+          <t>-4,07; 3,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 9,13</t>
+          <t>-7,7; 11,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 37,69</t>
+          <t>-3,57; 38,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 33,01</t>
+          <t>-7,04; 33,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 19,01</t>
+          <t>-18,97; 19,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 62,63</t>
+          <t>-32,43; 79,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,25</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-10,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>116,67%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.224233405196985</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.247704939710125</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4647684962583248</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.713638016731661</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1099176511175372</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.366123094623962</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.0240114881592606</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.166701948459532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-14,76; 7,37</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 16,47</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-12,16; 12,9</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-13,77; 34,14</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-54,71; 49,35</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-16,98; 138,16</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-48,97; 94,06</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-14.75928628960711</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.748301760641295</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-12.15595104540406</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-13.77484407748442</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5470967762952285</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1697757165825783</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4896506771213076</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.373370562915127</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16.46750514341565</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.89947794390747</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>34.13710486018294</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.4934890702200979</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.381574545592829</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.9405696213128851</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,57</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,29</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-10,36%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 8,8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,12; 8,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-6,11; 2,1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,29; 16,03</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-3,72; 53,61</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,57; 57,44</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-28,62; 12,23</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-36,7; 95,04</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.007408429465197</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.572085516841054</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.013334262433666</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.285042278750502</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2149809712718551</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2621835051440921</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1036212479950677</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1526429537434122</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6,24</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,84</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-26,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-34,17%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.7324730846023966</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1222656187460817</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-6.112319221637105</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.285247344578584</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.03718119770876002</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.005746780656377776</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2862471374691952</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3670385951711</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,53; 10,94</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-14,0; 0,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 11,76</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-19,73; 9,02</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-18,99; 55,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-49,54; 8,24</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-18,32; 69,64</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-79,29; 134,18</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.800315597794809</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.757786409576738</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.096263294098543</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16.03114085234116</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.536056734681044</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5744271026551825</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.122275275246093</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.950399242976582</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +815,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,16</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.819760613308525</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-6.241683799245681</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.407162541747633</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-5.842188630335738</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1141789481997839</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.264418754939545</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.1706487480118695</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.3417260180060597</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,62; 7,03</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,46; 5,68</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,07; 3,25</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,7; 11,65</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-3,57; 38,17</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-7,04; 33,52</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-18,97; 19,2</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-32,43; 79,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.533613898723558</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-14.00457468698456</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.088914423947199</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-19.73215303325416</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1898508074273749</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4953932376310746</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1832282860432752</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7928973402429719</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.94409796420685</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9631816553381921</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.75667297095654</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.017663614611548</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.5525499515633848</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.08236110069197118</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.6963972234842998</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.341777090093928</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3.160885807803901</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.252609145167353</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.5151060260099621</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.056856116247168</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1565604218233393</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1196096433851637</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.02633492532701259</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.05459059384139254</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.6196729782813745</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.458804383611365</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.070316105248943</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.700849886118738</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.03566520830684423</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.07035077035769569</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1897196751374538</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3242723249216224</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.029644984939849</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.677801669054445</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.247968513022306</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>11.64560670278817</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3816995516498995</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.33519642491143</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1920367156577792</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.7970117666297448</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1013,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
